--- a/outputs/step_disease_logistic/htn/htn_logistic_coefficients.xlsx
+++ b/outputs/step_disease_logistic/htn/htn_logistic_coefficients.xlsx
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2307</v>
+        <v>0.8397</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4237</v>
+        <v>2.3157</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9907</v>
+        <v>1.0139</v>
       </c>
       <c r="C3" t="n">
-        <v>2.693</v>
+        <v>2.7565</v>
       </c>
     </row>
     <row r="4">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5241</v>
+        <v>-0.3553</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5921</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="5">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5878</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8001</v>
+        <v>1.8154</v>
       </c>
     </row>
     <row r="6">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.5948</v>
+        <v>-1.435</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2029</v>
+        <v>0.2381</v>
       </c>
     </row>
   </sheetData>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.3355</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8018</v>
+        <v>2.4509</v>
       </c>
     </row>
     <row r="3">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9564</v>
+        <v>0.996</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6024</v>
+        <v>2.7075</v>
       </c>
     </row>
     <row r="4">
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.501</v>
+        <v>-0.3152</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6059</v>
+        <v>0.7297</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4061</v>
+        <v>0.4541</v>
       </c>
       <c r="C5" t="n">
-        <v>1.501</v>
+        <v>1.5747</v>
       </c>
     </row>
     <row r="6">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2753</v>
+        <v>0.2329</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3169</v>
+        <v>1.2623</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.6408</v>
+        <v>-1.4629</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1938</v>
+        <v>0.2316</v>
       </c>
     </row>
   </sheetData>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9306</v>
+        <v>0.5271</v>
       </c>
       <c r="C2" t="n">
-        <v>2.536</v>
+        <v>1.6941</v>
       </c>
     </row>
     <row r="3">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.866</v>
+        <v>0.8944</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3773</v>
+        <v>2.4458</v>
       </c>
     </row>
     <row r="4">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3718</v>
+        <v>-0.1831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6895</v>
+        <v>0.8327</v>
       </c>
     </row>
     <row r="5">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2418</v>
+        <v>0.2621</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2736</v>
+        <v>1.2997</v>
       </c>
     </row>
     <row r="6">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1859</v>
+        <v>0.1642</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2043</v>
+        <v>1.1784</v>
       </c>
     </row>
     <row r="7">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1904</v>
+        <v>0.1663</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2098</v>
+        <v>1.181</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.443</v>
+        <v>-0.4543</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6421</v>
+        <v>0.6349</v>
       </c>
     </row>
     <row r="9">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0448</v>
       </c>
       <c r="C9" t="n">
-        <v>1.009</v>
+        <v>1.0458</v>
       </c>
     </row>
     <row r="10">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.5229</v>
+        <v>-1.3424</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2181</v>
+        <v>0.2612</v>
       </c>
     </row>
   </sheetData>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2551</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5082</v>
+        <v>2.2867</v>
       </c>
     </row>
     <row r="3">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8451</v>
+        <v>0.8595</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3281</v>
+        <v>2.3619</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4424</v>
+        <v>-0.2823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6425</v>
+        <v>0.7541</v>
       </c>
     </row>
     <row r="5">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1744</v>
+        <v>0.1605</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1906</v>
+        <v>1.1741</v>
       </c>
     </row>
     <row r="6">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.54</v>
+        <v>0.652</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7161</v>
+        <v>1.9193</v>
       </c>
     </row>
     <row r="7">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0519</v>
+        <v>0.0343</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0532</v>
+        <v>1.0349</v>
       </c>
     </row>
     <row r="8">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.6158</v>
+        <v>-1.448</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1987</v>
+        <v>0.235</v>
       </c>
     </row>
   </sheetData>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.024</v>
+        <v>0.6322</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7843</v>
+        <v>1.8818</v>
       </c>
     </row>
     <row r="3">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8207</v>
+        <v>0.8385</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2721</v>
+        <v>2.313</v>
       </c>
     </row>
     <row r="4">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3664</v>
+        <v>-0.2012</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6932</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="5">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0292</v>
+        <v>0.0285</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0296</v>
+        <v>1.0289</v>
       </c>
     </row>
     <row r="6">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4037</v>
+        <v>0.5301</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4974</v>
+        <v>1.6991</v>
       </c>
     </row>
     <row r="7">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0665</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0761</v>
+        <v>1.0687</v>
       </c>
     </row>
     <row r="8">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.279</v>
+        <v>0.2089</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3219</v>
+        <v>1.2323</v>
       </c>
     </row>
     <row r="9">
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2995</v>
+        <v>-0.2754</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7412</v>
+        <v>0.7593</v>
       </c>
     </row>
     <row r="10">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1003</v>
+        <v>-0.0679</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1055</v>
+        <v>0.9344</v>
       </c>
     </row>
     <row r="11">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.5602</v>
+        <v>-1.3915</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2101</v>
+        <v>0.2487</v>
       </c>
     </row>
   </sheetData>
